--- a/SeleniumTests/TestDataFolder/SettingTestDataNegative.xlsx
+++ b/SeleniumTests/TestDataFolder/SettingTestDataNegative.xlsx
@@ -1,53 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290A8638-09D0-4075-BE51-0C297ECC6DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878D006E-25F6-4554-B226-789B25BCB309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31155" yWindow="990" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConsolidateDateTestData" sheetId="4" r:id="rId1"/>
     <sheet name="InvalidFileTestData" sheetId="2" r:id="rId2"/>
     <sheet name="WrongFileTypeTestData" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
-  <si>
-    <t>CutOffDate</t>
-  </si>
-  <si>
-    <t>ConsolidateCutOffDate</t>
-  </si>
-  <si>
-    <t>securityToken</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
   <si>
     <t>true</t>
   </si>
   <si>
-    <t>filePath</t>
-  </si>
-  <si>
     <t>@"C:\invalid_path\nonexistentfile.png"</t>
   </si>
   <si>
     <t>@"D:\e-invoice\SeleniumTests\ReceiptTest.txt"</t>
+  </si>
+  <si>
+    <t>B2C Cut Off Date</t>
+  </si>
+  <si>
+    <t>Consolidate Cut Off Date</t>
+  </si>
+  <si>
+    <t>Security Token</t>
+  </si>
+  <si>
+    <t>Auto Consolidate Cut Off Date</t>
+  </si>
+  <si>
+    <t>Import File Path</t>
   </si>
 </sst>
 </file>
@@ -368,16 +382,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8757100-4597-4449-A195-51F1B9078EF4}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -388,7 +407,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -403,16 +422,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -423,10 +442,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -441,16 +460,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -461,10 +480,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
